--- a/138_Cuenca_Chira/_raw_reportes_xlsx/IDConfig_803_completo.xlsx
+++ b/138_Cuenca_Chira/_raw_reportes_xlsx/IDConfig_803_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R649e83bf098a4c72"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R3d45a38ccac1445d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -174,7 +174,7 @@
       </x:c>
       <x:c s="" t="inlineStr">
         <x:is>
-          <x:t>Dpto: Piura / Prov: Ayabaca / Dist.: Paimas</x:t>
+          <x:t>Dpto: Piura / Prov: Ayabaca / Dist.: Paimás</x:t>
         </x:is>
       </x:c>
     </x:row>

--- a/138_Cuenca_Chira/_raw_reportes_xlsx/IDConfig_803_completo.xlsx
+++ b/138_Cuenca_Chira/_raw_reportes_xlsx/IDConfig_803_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R3d45a38ccac1445d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rdbd8e47b52834795"/>
   </x:sheets>
 </x:workbook>
 </file>
